--- a/Bracket_Generator/Farewell_2026_Seeding.xlsx
+++ b/Bracket_Generator/Farewell_2026_Seeding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\iiscshuttlers\Bracket_Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E25AE6-F257-40E4-A29A-90B0C437968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1AF0D4-60F3-41B1-8E86-9AB69FDAE343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{29488819-66B0-494A-B67C-22727C997863}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29488819-66B0-494A-B67C-22727C997863}"/>
   </bookViews>
   <sheets>
     <sheet name="MS" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -289,9 +289,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -301,14 +298,12 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,16 +669,16 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2">
         <v>3</v>
       </c>
     </row>
@@ -691,16 +686,16 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3">
         <v>4</v>
       </c>
     </row>
@@ -708,31 +703,30 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5">
         <v>5</v>
       </c>
     </row>
@@ -740,31 +734,30 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -772,16 +765,16 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8">
         <v>2</v>
       </c>
     </row>
@@ -857,138 +850,138 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1024,295 +1017,295 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
         <v>1</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
         <v>5</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <v>4</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
         <v>2</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
         <v>3</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1340,41 +1333,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1389,13 +1382,13 @@
       <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1407,58 +1400,58 @@
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
